--- a/MATERIAL_IN_OUT/obj/Release/Package/PackageTmp/Template/UploadMaterialInOut_B.xlsx
+++ b/MATERIAL_IN_OUT/obj/Release/Package/PackageTmp/Template/UploadMaterialInOut_B.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70L4853\Desktop\a\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70K6885\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255B5B2E-9995-452A-A143-2F2304E6A6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8235"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,22 +19,34 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master(Ko Xóa)'!$A$1:$H$50</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>NGUYEN THI_Dao</author>
+    <author>NGUYEN NHU_Minh</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +61,69 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{B7F063ED-3C25-4481-9644-CC0423F804D8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>NGUYEN NHU_Minh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Bộ phận tự điền</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{7D11D3F6-0A2D-4914-B7EA-3202FAC79F9B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>NGUYEN NHU_Minh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Bộ phận bắt buộc phải điền</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{9137FF87-FBC2-454A-A2C2-62011ADD6C96}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>NGUYEN NHU_Minh: Bộ phận tự điền</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -62,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -91,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="106">
   <si>
     <t>Sloc</t>
   </si>
@@ -388,13 +463,34 @@
   </si>
   <si>
     <t>Scrap mixing part560</t>
+  </si>
+  <si>
+    <t>STprice</t>
+  </si>
+  <si>
+    <t>Roh_Halb</t>
+  </si>
+  <si>
+    <t>NameCode</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>khong bat buoc</t>
+  </si>
+  <si>
+    <t>Halb</t>
+  </si>
+  <si>
+    <t>Namecost_costcentor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,8 +519,21 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,6 +543,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,16 +565,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -467,6 +578,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -746,105 +864,133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="4"/>
-    <col min="7" max="7" width="13.7109375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
-    <col min="12" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="7.42578125" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="O1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="P1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="Q1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="R1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="1">
         <v>2020</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="E2">
+      <c r="F2">
+        <v>120000</v>
+      </c>
+      <c r="G2">
         <v>5.1566453999999998E-2</v>
       </c>
-      <c r="F2" s="2">
-        <v>201</v>
-      </c>
-      <c r="G2" s="2" t="str">
-        <f>VLOOKUP(F2,'Master(Ko Xóa)'!$F$2:$H$158,3,0)</f>
+      <c r="H2" s="2">
+        <v>201</v>
+      </c>
+      <c r="I2" s="2" t="str">
+        <f>VLOOKUP(H2,'Master(Ko Xóa)'!$F$2:$H$158,3,0)</f>
         <v>Out</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>19</v>
       </c>
-      <c r="M2" t="s">
+      <c r="Q2" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="R2" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -852,14 +998,8 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'Master(Ko Xóa)'!$O$2:$O$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>'Master(Ko Xóa)'!$A$2:$A$25</xm:f>
           </x14:formula1>
@@ -872,7 +1012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2106,7 +2246,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H50"/>
+  <autoFilter ref="A1:H50" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MATERIAL_IN_OUT/obj/Release/Package/PackageTmp/Template/UploadMaterialInOut_B.xlsx
+++ b/MATERIAL_IN_OUT/obj/Release/Package/PackageTmp/Template/UploadMaterialInOut_B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70K6885\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\MATERIAL_IN_OUT\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255B5B2E-9995-452A-A143-2F2304E6A6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B50FC86-9D6E-4E66-8B16-41C249E605DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,6 +123,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{FE91CE3B-660D-4022-A44D-CBF4FF2040C8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>NGUYEN NHU_Minh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Bắt buộc phải nhập</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
@@ -477,13 +501,13 @@
     <t>Reason</t>
   </si>
   <si>
-    <t>khong bat buoc</t>
-  </si>
-  <si>
     <t>Halb</t>
   </si>
   <si>
     <t>Namecost_costcentor</t>
+  </si>
+  <si>
+    <t>bat buoc</t>
   </si>
 </sst>
 </file>
@@ -948,7 +972,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D2" s="1">
         <v>2020</v>
@@ -976,10 +1000,10 @@
         <v>7</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="N2" t="s">
         <v>16</v>

--- a/MATERIAL_IN_OUT/obj/Release/Package/PackageTmp/Template/UploadMaterialInOut_B.xlsx
+++ b/MATERIAL_IN_OUT/obj/Release/Package/PackageTmp/Template/UploadMaterialInOut_B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\MATERIAL_IN_OUT\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70K6885\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B50FC86-9D6E-4E66-8B16-41C249E605DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2777DEB0-1593-4A42-A5C6-857404FBC855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,7 +170,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>B1: Chọn MvType sẽ lọc theo TypeRQ.</t>
+          <t>B1: Chọn MvType theo TypeRQ.</t>
         </r>
         <r>
           <rPr>
@@ -1040,7 +1040,8 @@
   <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1150,7 +1151,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1178,7 +1179,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1202,7 +1203,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -1230,7 +1231,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -1254,7 +1255,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1282,7 +1283,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1306,7 +1307,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1334,7 +1335,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1358,7 +1359,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -1386,7 +1387,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1410,7 +1411,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -1438,7 +1439,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
+        <v>13.1</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -1462,7 +1463,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -1490,7 +1491,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>13.3</v>
       </c>
       <c r="D18">
         <v>9</v>
@@ -1514,7 +1515,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>13.4</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -1542,7 +1543,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -1566,7 +1567,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>15.1</v>
       </c>
       <c r="D21">
         <v>10</v>
@@ -1594,7 +1595,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>15.2</v>
       </c>
       <c r="D22">
         <v>11</v>
@@ -1618,7 +1619,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="D23">
         <v>11</v>
@@ -1646,7 +1647,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>16.2</v>
       </c>
       <c r="D24">
         <v>12</v>
@@ -1670,7 +1671,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>25</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="D25">
         <v>12</v>
@@ -1697,6 +1698,9 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>17.2</v>
+      </c>
       <c r="D26">
         <v>13</v>
       </c>
@@ -1718,6 +1722,9 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>18.100000000000001</v>
+      </c>
       <c r="D27">
         <v>13</v>
       </c>
@@ -1743,6 +1750,9 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>18.2</v>
+      </c>
       <c r="D28">
         <v>14</v>
       </c>
@@ -1764,6 +1774,9 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>19</v>
+      </c>
       <c r="D29">
         <v>14</v>
       </c>
@@ -1789,6 +1802,9 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>20</v>
+      </c>
       <c r="D30">
         <v>15</v>
       </c>
@@ -1810,6 +1826,9 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>21</v>
+      </c>
       <c r="D31">
         <v>15</v>
       </c>
@@ -1835,6 +1854,9 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>22</v>
+      </c>
       <c r="D32">
         <v>16</v>
       </c>
@@ -1855,7 +1877,10 @@
         <v>201</v>
       </c>
     </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>23</v>
+      </c>
       <c r="D33">
         <v>16</v>
       </c>
@@ -1880,7 +1905,10 @@
         <v>202</v>
       </c>
     </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>24</v>
+      </c>
       <c r="D34">
         <v>16</v>
       </c>
@@ -1901,7 +1929,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D35">
         <v>17</v>
       </c>
@@ -1926,7 +1954,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D36">
         <v>17</v>
       </c>
@@ -1947,7 +1975,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D37">
         <v>18</v>
       </c>
@@ -1972,7 +2000,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D38">
         <v>18</v>
       </c>
@@ -1993,7 +2021,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D39">
         <v>19</v>
       </c>
@@ -2014,7 +2042,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>19</v>
       </c>
@@ -2039,7 +2067,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D41">
         <v>20</v>
       </c>
@@ -2060,7 +2088,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D42">
         <v>20</v>
       </c>
@@ -2085,7 +2113,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D43">
         <v>21</v>
       </c>
@@ -2106,7 +2134,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D44">
         <v>21</v>
       </c>
@@ -2131,7 +2159,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D45">
         <v>22</v>
       </c>
@@ -2152,7 +2180,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="46" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D46">
         <v>22</v>
       </c>
@@ -2177,7 +2205,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="47" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D47">
         <v>23</v>
       </c>
@@ -2198,7 +2226,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D48">
         <v>23</v>
       </c>
